--- a/partner_results/unknown_complete/ClassMoreThanOneGermanDefinition_unknown.xlsx
+++ b/partner_results/unknown_complete/ClassMoreThanOneGermanDefinition_unknown.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ultrasonic cleaner</t>
+          <t>microtome</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>cleaning device</t>
+          <t>device</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ein Gerät, das Ultraschall und ein Reinigungsmittel verwendet, um empfindliche oder komplexe Gegenstände zu reinigen. | Ein Ultraschallreiniger ist ein Reinigungsgerät, das Hochfrequenzschallwellen und ein Reinigungsmittel verwendet, um Verunreinigungen von empfindlichen oder komplexen Gegenständen zu entfernen.</t>
+          <t>Ein Gerät, das verwendet wird, um extrem dünne Scheiben von Material zu schneiden, oft für mikroskopische Untersuchungen. | Ein Mikrotom ist ein Messgerät, das extrem dünne Scheiben von Material schneidet, oft zur Untersuchung unter einem Mikroskop.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -465,18 +465,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>microtome</t>
+          <t>ultrasonic cleaner</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>device</t>
+          <t>cleaning device</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Ein Mikrotom ist ein Messgerät, das extrem dünne Scheiben von Material schneidet, oft zur Untersuchung unter einem Mikroskop. | Ein Gerät, das verwendet wird, um extrem dünne Scheiben von Material zu schneiden, oft für mikroskopische Untersuchungen.</t>
+          <t>Ein Gerät, das Ultraschall und ein Reinigungsmittel verwendet, um empfindliche oder komplexe Gegenstände zu reinigen. | Ein Ultraschallreiniger ist ein Reinigungsgerät, das Hochfrequenzschallwellen und ein Reinigungsmittel verwendet, um Verunreinigungen von empfindlichen oder komplexen Gegenständen zu entfernen.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -510,7 +510,7 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ein Kryogefrierschrank ist ein Temperaturwechselgerät, das Materialien bei extrem niedrigen Temperaturen konserviert, oft unter -150°C. | Ein Gerät, das verwendet wird, um Materialien bei extrem niedrigen Temperaturen zu konservieren, typischerweise unter -150°C.</t>
+          <t>Ein Gerät, das verwendet wird, um Materialien bei extrem niedrigen Temperaturen zu konservieren, typischerweise unter -150°C. | Ein Kryogefrierschrank ist ein Temperaturwechselgerät, das Materialien bei extrem niedrigen Temperaturen konserviert, oft unter -150°C.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
